--- a/output/yearly_surface_area_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_45_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631756467</v>
+        <v>10.84497629454084</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907189086056</v>
+        <v>37.78907181063455</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.905212441044564</v>
+        <v>4.813508993922111</v>
       </c>
       <c r="C2" t="n">
-        <v>6.257659866869169</v>
+        <v>6.848671984825748</v>
       </c>
       <c r="D2" t="n">
-        <v>36.89996921182061</v>
+        <v>14.61527807312227</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.30606860401353</v>
+        <v>17.32293824143497</v>
       </c>
       <c r="C3" t="n">
-        <v>20.08164929036851</v>
+        <v>17.88253443285565</v>
       </c>
       <c r="D3" t="n">
-        <v>83.91979375901735</v>
+        <v>54.17774705886023</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.86248287260999</v>
+        <v>33.45108952680157</v>
       </c>
       <c r="C4" t="n">
-        <v>80.97945938479815</v>
+        <v>43.6740283711236</v>
       </c>
       <c r="D4" t="n">
-        <v>80.14988257470961</v>
+        <v>64.50278766442393</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.76831720846032</v>
+        <v>40.84070449666732</v>
       </c>
       <c r="C5" t="n">
-        <v>136.0702318086079</v>
+        <v>103.0589652533089</v>
       </c>
       <c r="D5" t="n">
-        <v>55.83690067903736</v>
+        <v>47.66385104118265</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.92713935237005</v>
+        <v>38.11831811279092</v>
       </c>
       <c r="C6" t="n">
-        <v>127.5172458092097</v>
+        <v>158.5915241440298</v>
       </c>
       <c r="D6" t="n">
-        <v>42.2642386678252</v>
+        <v>39.28561613314037</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.87774886752143</v>
+        <v>26.64954143177966</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6275771005171</v>
+        <v>175.2881073501552</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.77315952705676</v>
+        <v>13.93590866178347</v>
       </c>
       <c r="C8" t="n">
-        <v>65.67401267559038</v>
+        <v>123.3369640845268</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>39.82655911818034</v>
+        <v>59.01874498850123</v>
       </c>
       <c r="D9" t="n">
         <v>33.83593462686631</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.688984161509818</v>
+        <v>7.660762961016333</v>
       </c>
       <c r="C21" t="n">
-        <v>94.19005597849527</v>
+        <v>92.88675090232304</v>
       </c>
       <c r="D21" t="n">
-        <v>8.650107181698546</v>
+        <v>7.660762961016333</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.050912011900593</v>
+        <v>6.044620615047611</v>
       </c>
       <c r="C2" t="n">
-        <v>7.659595588533614</v>
+        <v>5.884595739255381</v>
       </c>
       <c r="D2" t="n">
-        <v>31.78997241121597</v>
+        <v>17.62924352515997</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.38460842035327</v>
+        <v>16.60135367881356</v>
       </c>
       <c r="C3" t="n">
-        <v>22.09423208407447</v>
+        <v>22.17768063893545</v>
       </c>
       <c r="D3" t="n">
-        <v>91.95539871827749</v>
+        <v>53.10273332270997</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.39477005476101</v>
+        <v>32.82571623919635</v>
       </c>
       <c r="C4" t="n">
-        <v>64.97500831016664</v>
+        <v>43.6612656509684</v>
       </c>
       <c r="D4" t="n">
-        <v>100.2384040990078</v>
+        <v>74.99374363200535</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.4070751110265</v>
+        <v>45.3076565509903</v>
       </c>
       <c r="C5" t="n">
-        <v>142.279786037969</v>
+        <v>92.11247835095699</v>
       </c>
       <c r="D5" t="n">
-        <v>68.69779560467057</v>
+        <v>57.48132808365076</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.78250364467628</v>
+        <v>45.68562941712533</v>
       </c>
       <c r="C6" t="n">
-        <v>167.2456301569654</v>
+        <v>160.0808354113722</v>
       </c>
       <c r="D6" t="n">
-        <v>49.26802678992194</v>
+        <v>44.71958967614647</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.75903951076558</v>
+        <v>35.09355343600648</v>
       </c>
       <c r="C7" t="n">
-        <v>140.434100353985</v>
+        <v>201.9376487819349</v>
       </c>
       <c r="D7" t="n">
-        <v>41.50142070162541</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.2849121228766</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="C8" t="n">
-        <v>96.96722074845746</v>
+        <v>172.9888542268092</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>10.42812411450962</v>
       </c>
       <c r="C9" t="n">
-        <v>59.3515574602409</v>
+        <v>102.1734288240783</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>38.15071578703105</v>
+        <v>49.39663573917827</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.866332985181155</v>
+        <v>7.838115205283971</v>
       </c>
       <c r="C21" t="n">
-        <v>102.262328807355</v>
+        <v>100.9157332680311</v>
       </c>
       <c r="D21" t="n">
-        <v>9.832916231476444</v>
+        <v>8.817879605944468</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.85576520293373</v>
+        <v>7.239407571115979</v>
       </c>
       <c r="C2" t="n">
-        <v>14.22945122535327</v>
+        <v>8.154396431474007</v>
       </c>
       <c r="D2" t="n">
-        <v>29.66448863152162</v>
+        <v>23.76713017211103</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.83759502263855</v>
+        <v>17.95616551067416</v>
       </c>
       <c r="C3" t="n">
-        <v>25.45180923259856</v>
+        <v>22.3003991019663</v>
       </c>
       <c r="D3" t="n">
-        <v>94.10542619057802</v>
+        <v>53.90776644019236</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.27165068110266</v>
+        <v>31.86851222755571</v>
       </c>
       <c r="C4" t="n">
-        <v>60.36766633413637</v>
+        <v>48.37070938824035</v>
       </c>
       <c r="D4" t="n">
-        <v>116.2173297333289</v>
+        <v>81.06879842588461</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.11884219660543</v>
+        <v>46.55938487390499</v>
       </c>
       <c r="C5" t="n">
-        <v>130.7933378982814</v>
+        <v>85.85383673638358</v>
       </c>
       <c r="D5" t="n">
-        <v>84.45484625783187</v>
+        <v>68.20692175254716</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.70578845502478</v>
+        <v>51.88438442173969</v>
       </c>
       <c r="C6" t="n">
-        <v>190.752597187451</v>
+        <v>154.8883718036108</v>
       </c>
       <c r="D6" t="n">
-        <v>56.63407981488576</v>
+        <v>50.35482149852316</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.04146405441917</v>
+        <v>43.05847256056086</v>
       </c>
       <c r="C7" t="n">
-        <v>183.9117791842592</v>
+        <v>214.3940636534184</v>
       </c>
       <c r="D7" t="n">
-        <v>45.39405034896402</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.21390749300134</v>
+        <v>27.87181732356695</v>
       </c>
       <c r="C8" t="n">
-        <v>133.6845848872882</v>
+        <v>215.3807200961865</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.41718602104266</v>
+        <v>14.75468624712531</v>
       </c>
       <c r="C9" t="n">
-        <v>84.64530531245572</v>
+        <v>148.656237377052</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>51.81664383014665</v>
+        <v>78.43673283079892</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>43.35790561035613</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.027792865719928</v>
+        <v>8.001187999613997</v>
       </c>
       <c r="C21" t="n">
-        <v>110.382151903649</v>
+        <v>109.0161864947407</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0382151903649</v>
+        <v>10.0014849995175</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.817076131840604</v>
+        <v>6.563965150594174</v>
       </c>
       <c r="C2" t="n">
-        <v>9.789006359044945</v>
+        <v>5.544911033585985</v>
       </c>
       <c r="D2" t="n">
-        <v>24.63499514266521</v>
+        <v>19.42682357163588</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.01984024272996</v>
+        <v>21.91260875878881</v>
       </c>
       <c r="C3" t="n">
-        <v>41.98444057211485</v>
+        <v>33.80157345721769</v>
       </c>
       <c r="D3" t="n">
-        <v>99.55412594914782</v>
+        <v>59.25829142833748</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.99766095615978</v>
+        <v>22.36028571192535</v>
       </c>
       <c r="C4" t="n">
-        <v>98.32399607572655</v>
+        <v>69.78655380868027</v>
       </c>
       <c r="D4" t="n">
-        <v>106.2113571316454</v>
+        <v>77.43142318165017</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.7538687303371</v>
+        <v>29.23153789394879</v>
       </c>
       <c r="C5" t="n">
-        <v>113.9809084630547</v>
+        <v>92.55426481786806</v>
       </c>
       <c r="D5" t="n">
-        <v>56.52412407201012</v>
+        <v>48.40016181936777</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.28182801104362</v>
+        <v>26.72709950041517</v>
       </c>
       <c r="C6" t="n">
-        <v>121.1172325252248</v>
+        <v>141.2028088064103</v>
       </c>
       <c r="D6" t="n">
-        <v>29.86672865859647</v>
+        <v>28.09565580013523</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.63713856452295</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>93.96209102575797</v>
+        <v>151.4532365864512</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>62.33607048115122</v>
+        <v>109.5679525324653</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>59.79530742256046</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>26.68684784454105</v>
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.165956419746716</v>
+        <v>3.911282853719293</v>
       </c>
       <c r="C2" t="n">
-        <v>4.704534998750716</v>
+        <v>2.720422888467912</v>
       </c>
       <c r="D2" t="n">
-        <v>17.87860744203866</v>
+        <v>13.83282515283756</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.17615911188346</v>
+        <v>22.82072538521711</v>
       </c>
       <c r="C3" t="n">
-        <v>40.92415305152829</v>
+        <v>28.18106785040469</v>
       </c>
       <c r="D3" t="n">
-        <v>97.98332962235291</v>
+        <v>60.99598486485433</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4548365911693</v>
+        <v>30.78368101436299</v>
       </c>
       <c r="C4" t="n">
-        <v>105.0371868773663</v>
+        <v>78.68216975686063</v>
       </c>
       <c r="D4" t="n">
-        <v>125.9680479319082</v>
+        <v>88.33078619419827</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.58268477689965</v>
+        <v>32.64311116620645</v>
       </c>
       <c r="C5" t="n">
-        <v>146.2558642401686</v>
+        <v>112.2628499806228</v>
       </c>
       <c r="D5" t="n">
-        <v>74.31830121148356</v>
+        <v>60.37748381117885</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.35982804803563</v>
+        <v>31.67805317293184</v>
       </c>
       <c r="C6" t="n">
-        <v>151.225471119066</v>
+        <v>152.0707558924225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.38749691020379</v>
+        <v>33.48937768726721</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>124.9833549845487</v>
+        <v>180.7976754663884</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>30.24273802932299</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>82.11337798320321</v>
+        <v>142.36323459283</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>44.48593372253571</v>
+        <v>66.00780689503428</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.151230204183014</v>
+        <v>3.752239725631309</v>
       </c>
       <c r="C2" t="n">
-        <v>9.770353152664256</v>
+        <v>9.803732574608649</v>
       </c>
       <c r="D2" t="n">
-        <v>16.24596100987622</v>
+        <v>15.21316242500857</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.84036033930204</v>
+        <v>18.00034415736527</v>
       </c>
       <c r="C3" t="n">
-        <v>28.84374755077129</v>
+        <v>18.64338890364693</v>
       </c>
       <c r="D3" t="n">
-        <v>90.2275227588031</v>
+        <v>58.55634181980101</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.31216437888403</v>
+        <v>37.2288546927433</v>
       </c>
       <c r="C4" t="n">
-        <v>104.5266780711579</v>
+        <v>74.3428449040897</v>
       </c>
       <c r="D4" t="n">
-        <v>143.1466692608189</v>
+        <v>96.25643541058277</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.23402547317179</v>
+        <v>38.9508401659922</v>
       </c>
       <c r="C5" t="n">
-        <v>168.8851488230576</v>
+        <v>129.737959116216</v>
       </c>
       <c r="D5" t="n">
-        <v>97.83115872819468</v>
+        <v>76.40451508300804</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.55858305264999</v>
+        <v>37.39378830705677</v>
       </c>
       <c r="C6" t="n">
-        <v>188.9010210172416</v>
+        <v>165.0317890838888</v>
       </c>
       <c r="D6" t="n">
-        <v>48.18123208132072</v>
+        <v>43.06927178530758</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.84160412891355</v>
+        <v>25.75124228239384</v>
       </c>
       <c r="C7" t="n">
-        <v>169.2395597442907</v>
+        <v>202.5365148815255</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>119.8321247803657</v>
+        <v>188.7606310955342</v>
       </c>
       <c r="D8" t="n">
         <v>29.29044275620359</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>69.33593161243097</v>
+        <v>114.3765527878661</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.28601704376787</v>
+        <v>52.52841091572559</v>
       </c>
       <c r="D10" t="n">
         <v>30.32127784566274</v>
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.102322745419921</v>
+        <v>2.201078352921349</v>
       </c>
       <c r="C2" t="n">
-        <v>4.665265090580843</v>
+        <v>4.524875168873549</v>
       </c>
       <c r="D2" t="n">
-        <v>11.32347802078271</v>
+        <v>10.47524800431347</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.69800692218626</v>
+        <v>17.69109363052752</v>
       </c>
       <c r="C3" t="n">
-        <v>34.57224540505143</v>
+        <v>28.49522711576367</v>
       </c>
       <c r="D3" t="n">
-        <v>87.26755343049898</v>
+        <v>59.11102927270046</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.89398091460389</v>
+        <v>41.03214529899544</v>
       </c>
       <c r="C4" t="n">
-        <v>103.0206770928433</v>
+        <v>71.22874118621884</v>
       </c>
       <c r="D4" t="n">
-        <v>154.046032273367</v>
+        <v>103.6971012610693</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.32023934469627</v>
+        <v>40.37437433715008</v>
       </c>
       <c r="C5" t="n">
-        <v>201.3073667558085</v>
+        <v>153.5698846368073</v>
       </c>
       <c r="D5" t="n">
-        <v>104.0652566501619</v>
+        <v>82.54043823455059</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.8302651248191</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="C6" t="n">
-        <v>224.0809682512218</v>
+        <v>208.5840807396859</v>
       </c>
       <c r="D6" t="n">
-        <v>47.53720558733482</v>
+        <v>42.78751019418875</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>169.2395597442907</v>
+        <v>225.2335400560075</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>87.45408549430587</v>
+        <v>143.4480658060227</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>40.04843409934012</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.353069320630357</v>
+        <v>2.980586030093316</v>
       </c>
       <c r="C2" t="n">
-        <v>6.739697989654353</v>
+        <v>8.17206789015045</v>
       </c>
       <c r="D2" t="n">
-        <v>13.31740760810798</v>
+        <v>15.1905822278109</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.75843331149305</v>
+        <v>12.73817646260236</v>
       </c>
       <c r="C3" t="n">
-        <v>26.39919576719673</v>
+        <v>22.81581664669588</v>
       </c>
       <c r="D3" t="n">
-        <v>78.06857744170637</v>
+        <v>54.22192570555134</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.68603032775282</v>
+        <v>37.68831261833081</v>
       </c>
       <c r="C4" t="n">
-        <v>94.81424803304421</v>
+        <v>71.82858903351364</v>
       </c>
       <c r="D4" t="n">
-        <v>160.5422568323682</v>
+        <v>108.7000875619111</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.1930951692297</v>
+        <v>49.84823968313181</v>
       </c>
       <c r="C5" t="n">
-        <v>197.625812864883</v>
+        <v>144.1941940612503</v>
       </c>
       <c r="D5" t="n">
-        <v>128.5598618711198</v>
+        <v>97.9784208838317</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.37619896383834</v>
+        <v>41.13719230334986</v>
       </c>
       <c r="C6" t="n">
-        <v>268.03577646576</v>
+        <v>227.3413523770254</v>
       </c>
       <c r="D6" t="n">
-        <v>63.4366096576119</v>
+        <v>55.94980166502573</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>18.02586959767568</v>
       </c>
       <c r="C7" t="n">
-        <v>236.7916557781052</v>
+        <v>264.5790427991069</v>
       </c>
       <c r="D7" t="n">
-        <v>38.50709020367265</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>141.4453004893592</v>
+        <v>209.6227698107789</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7952820603647</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3058,7 +3058,7 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>58.3531200450219</v>
+        <v>91.30155474724909</v>
       </c>
       <c r="D9" t="n">
         <v>32.50468473990763</v>
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3173,7 +3173,7 @@
         <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.913827186204533</v>
+        <v>1.97920337176157</v>
       </c>
       <c r="C2" t="n">
-        <v>4.014366362665207</v>
+        <v>3.986877426946297</v>
       </c>
       <c r="D2" t="n">
-        <v>9.727156253677396</v>
+        <v>11.8811107167949</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.05648370295658</v>
+        <v>11.77606371244049</v>
       </c>
       <c r="C3" t="n">
-        <v>26.81152980298039</v>
+        <v>27.29749491658256</v>
       </c>
       <c r="D3" t="n">
-        <v>73.18929135159971</v>
+        <v>53.87831400906496</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.78514578815274</v>
+        <v>33.14478424307656</v>
       </c>
       <c r="C4" t="n">
-        <v>84.3488175057732</v>
+        <v>67.11914529624168</v>
       </c>
       <c r="D4" t="n">
-        <v>162.4949530161151</v>
+        <v>110.7676482270549</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.13266877992289</v>
+        <v>54.41336650787948</v>
       </c>
       <c r="C5" t="n">
-        <v>195.6623174563894</v>
+        <v>144.439630987312</v>
       </c>
       <c r="D5" t="n">
-        <v>144.9059611468292</v>
+        <v>109.6612185643687</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.4667817945363</v>
+        <v>48.98626519880311</v>
       </c>
       <c r="C6" t="n">
-        <v>296.050928954147</v>
+        <v>239.7791140421282</v>
       </c>
       <c r="D6" t="n">
-        <v>77.24292762243481</v>
+        <v>65.40894079544375</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>290.9890377910503</v>
+        <v>301.3494213139669</v>
       </c>
       <c r="D7" t="n">
-        <v>42.63926629084747</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>183.6702692490145</v>
+        <v>257.1884460815369</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>34.88149593188918</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>66.89530681967339</v>
+        <v>107.8312408436526</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3470,7 +3470,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.073271224920016</v>
+        <v>2.988440011727291</v>
       </c>
       <c r="C2" t="n">
-        <v>7.317947387455725</v>
+        <v>8.737554567796613</v>
       </c>
       <c r="D2" t="n">
-        <v>19.22654703996954</v>
+        <v>13.04448174632737</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.08669689760998</v>
+        <v>9.326603190344699</v>
       </c>
       <c r="C3" t="n">
-        <v>21.73589417202438</v>
+        <v>21.48554850744145</v>
       </c>
       <c r="D3" t="n">
-        <v>65.55620295108076</v>
+        <v>51.56629816556372</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.29717612141307</v>
+        <v>28.00140802052752</v>
       </c>
       <c r="C4" t="n">
-        <v>76.55079549094079</v>
+        <v>67.41268785981148</v>
       </c>
       <c r="D4" t="n">
-        <v>161.5505117246296</v>
+        <v>110.5506819844163</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.05903770210439</v>
+        <v>53.18618187757097</v>
       </c>
       <c r="C5" t="n">
-        <v>178.4081015542516</v>
+        <v>134.9412219487241</v>
       </c>
       <c r="D5" t="n">
-        <v>163.0192062901829</v>
+        <v>121.1967540892688</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.53598715991909</v>
+        <v>58.48565598509524</v>
       </c>
       <c r="C6" t="n">
-        <v>302.8937104527472</v>
+        <v>238.8130743011494</v>
       </c>
       <c r="D6" t="n">
-        <v>96.24170919501908</v>
+        <v>79.89953691012668</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.23706852727577</v>
+        <v>31.08115056874977</v>
       </c>
       <c r="C7" t="n">
-        <v>345.0666465840774</v>
+        <v>322.3696214095954</v>
       </c>
       <c r="D7" t="n">
-        <v>50.66407202536089</v>
+        <v>47.60985491744906</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>261.4443223794468</v>
+        <v>318.6065824592173</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>122.3640521096182</v>
+        <v>185.7093592307351</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>68.18728679846222</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.04714925199963</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.671957398061323</v>
+        <v>5.293583621298801</v>
       </c>
       <c r="C2" t="n">
-        <v>6.397068040872216</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="D2" t="n">
-        <v>5.442809272344316</v>
+        <v>7.3719435111893</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.946224860444678</v>
+        <v>2.114684554947629</v>
       </c>
       <c r="C2" t="n">
-        <v>4.273547756586366</v>
+        <v>4.893030557966103</v>
       </c>
       <c r="D2" t="n">
-        <v>14.30406405087603</v>
+        <v>9.600510799829559</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.41620427333842</v>
+        <v>12.772537632251</v>
       </c>
       <c r="C3" t="n">
-        <v>26.89006961932013</v>
+        <v>28.63267179435823</v>
       </c>
       <c r="D3" t="n">
-        <v>72.49225048158448</v>
+        <v>56.53394154905258</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.02160811615598</v>
+        <v>39.55166976099125</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6490366812903</v>
+        <v>92.03197503920875</v>
       </c>
       <c r="D4" t="n">
-        <v>164.5752764014141</v>
+        <v>113.2180904968549</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.65631585471817</v>
+        <v>34.90113088597411</v>
       </c>
       <c r="C5" t="n">
-        <v>259.623180388069</v>
+        <v>202.1173086118121</v>
       </c>
       <c r="D5" t="n">
-        <v>146.6976507070797</v>
+        <v>112.287393673229</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.60884780754905</v>
+        <v>19.28054316370311</v>
       </c>
       <c r="C6" t="n">
-        <v>283.6534189449182</v>
+        <v>261.4747565582786</v>
       </c>
       <c r="D6" t="n">
-        <v>75.23034482872885</v>
+        <v>66.41523219229674</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>183.8518925743002</v>
+        <v>224.0358078568264</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>90.12443924985719</v>
+        <v>136.8556299720053</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>24.61732368398877</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>52.02968308196819</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.094108910887452</v>
+        <v>6.318528224532471</v>
       </c>
       <c r="C2" t="n">
-        <v>4.703553251046468</v>
+        <v>10.82573193472958</v>
       </c>
       <c r="D2" t="n">
-        <v>16.33137306014569</v>
+        <v>9.192103754862885</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.17152811080271</v>
+        <v>11.24591995214721</v>
       </c>
       <c r="C3" t="n">
-        <v>16.3755517068368</v>
+        <v>35.46072707739479</v>
       </c>
       <c r="D3" t="n">
-        <v>7.706719478337462</v>
+        <v>9.326603190344699</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39882469862875</v>
+        <v>13.39741204648255</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1467881281152</v>
+        <v>70.13939247864393</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576332317485735</v>
+        <v>1.576166123115594</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.544911033585985</v>
+        <v>4.777184328864979</v>
       </c>
       <c r="C2" t="n">
-        <v>6.107452468119408</v>
+        <v>9.078221021170256</v>
       </c>
       <c r="D2" t="n">
-        <v>13.65512881836889</v>
+        <v>10.18366893615216</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.38599107868502</v>
+        <v>17.58310138306037</v>
       </c>
       <c r="C3" t="n">
-        <v>17.60764507566654</v>
+        <v>39.68715094417731</v>
       </c>
       <c r="D3" t="n">
-        <v>19.5613230071177</v>
+        <v>14.7900291644782</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.43838355990859</v>
+        <v>13.13283903970958</v>
       </c>
       <c r="C4" t="n">
-        <v>25.48715214995145</v>
+        <v>54.57339138367169</v>
       </c>
       <c r="D4" t="n">
-        <v>19.10579207234717</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44251545759247</v>
+        <v>15.43790382913611</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15298097393692</v>
+        <v>86.12725294149621</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25105588580894</v>
+        <v>3.250085016660234</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.446736263161304</v>
+        <v>4.771293842639499</v>
       </c>
       <c r="C2" t="n">
-        <v>7.401395942316704</v>
+        <v>4.18911745402114</v>
       </c>
       <c r="D2" t="n">
-        <v>15.81202852459913</v>
+        <v>13.15247399379452</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.72331137831842</v>
+        <v>17.15113239319178</v>
       </c>
       <c r="C3" t="n">
-        <v>21.34319509032566</v>
+        <v>37.06097583531709</v>
       </c>
       <c r="D3" t="n">
-        <v>25.94268308472197</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.40530723760046</v>
+        <v>24.61928717939726</v>
       </c>
       <c r="C4" t="n">
-        <v>36.45032876327557</v>
+        <v>79.97120449253669</v>
       </c>
       <c r="D4" t="n">
-        <v>24.61928717939726</v>
+        <v>22.89631995844411</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.45623494503429</v>
+        <v>11.65825398793088</v>
       </c>
       <c r="C5" t="n">
-        <v>29.08427573831176</v>
+        <v>59.78843518863076</v>
       </c>
       <c r="D5" t="n">
-        <v>29.32971266437347</v>
+        <v>29.84513020910304</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73832719829037</v>
+        <v>16.72575625013592</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1037959095713</v>
+        <v>102.0271131258291</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021498159487112</v>
+        <v>4.181439062533979</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.997496725243765</v>
+        <v>4.390375733391736</v>
       </c>
       <c r="C2" t="n">
-        <v>9.895035111103601</v>
+        <v>5.732424845097126</v>
       </c>
       <c r="D2" t="n">
-        <v>18.82501222893259</v>
+        <v>15.620587722271</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1440802328128</v>
+        <v>16.66516727958961</v>
       </c>
       <c r="C3" t="n">
-        <v>25.59416264971435</v>
+        <v>25.2260072606218</v>
       </c>
       <c r="D3" t="n">
-        <v>32.18659848373168</v>
+        <v>25.15728492132452</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.30619177720055</v>
+        <v>29.21386643527233</v>
       </c>
       <c r="C4" t="n">
-        <v>45.57567367424968</v>
+        <v>86.95241241743575</v>
       </c>
       <c r="D4" t="n">
-        <v>31.43457974227862</v>
+        <v>27.26117025152543</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.15790681613028</v>
+        <v>23.88101290580367</v>
       </c>
       <c r="C5" t="n">
-        <v>50.11822030179968</v>
+        <v>105.7833151325938</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71045084717198</v>
+        <v>31.09685853201772</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.71952325622168</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>30.10823859384119</v>
+        <v>54.94351026817275</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.7623035490478</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06773901839734</v>
+        <v>18.04159931834449</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8704878819255</v>
+        <v>117.6999574577712</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882948197484702</v>
+        <v>6.013866439448162</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.847690237121502</v>
+        <v>6.627778751370216</v>
       </c>
       <c r="C2" t="n">
-        <v>12.99146737029804</v>
+        <v>4.920519493685013</v>
       </c>
       <c r="D2" t="n">
-        <v>27.55863980591221</v>
+        <v>27.34756404949915</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.9758004647591</v>
+        <v>13.95063487734718</v>
       </c>
       <c r="C3" t="n">
-        <v>30.95941385342317</v>
+        <v>22.08932334555324</v>
       </c>
       <c r="D3" t="n">
-        <v>37.00207097306228</v>
+        <v>29.57024085191393</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.92108463522854</v>
+        <v>22.21989579021806</v>
       </c>
       <c r="C4" t="n">
-        <v>46.45630136495907</v>
+        <v>61.65670106981243</v>
       </c>
       <c r="D4" t="n">
-        <v>34.62525978108076</v>
+        <v>29.09900195387546</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.7645858396258</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C5" t="n">
-        <v>51.12451169865266</v>
+        <v>99.20560551414022</v>
       </c>
       <c r="D5" t="n">
-        <v>29.15790681613028</v>
+        <v>27.16986771503048</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.4503444588088</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>37.75605320992383</v>
+        <v>76.43789450495242</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>31.85967649821749</v>
       </c>
       <c r="D7" t="n">
-        <v>30.66194429903638</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
         <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063006098600534</v>
+        <v>7.046665722599699</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21568217438001</v>
+        <v>66.06249114937218</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297254573950401</v>
+        <v>4.404166076624812</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.647012794827654</v>
+        <v>4.808600255400877</v>
       </c>
       <c r="C2" t="n">
-        <v>4.786020058203201</v>
+        <v>2.64090132442392</v>
       </c>
       <c r="D2" t="n">
-        <v>37.02661466566845</v>
+        <v>21.83505069015331</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.71135047941821</v>
+        <v>19.48769192929919</v>
       </c>
       <c r="C3" t="n">
-        <v>43.9528447191297</v>
+        <v>20.25836387713293</v>
       </c>
       <c r="D3" t="n">
-        <v>51.9540885087412</v>
+        <v>45.39601384437251</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91956310817654</v>
+        <v>25.52544031041707</v>
       </c>
       <c r="C4" t="n">
-        <v>66.3916702473948</v>
+        <v>57.85341046356029</v>
       </c>
       <c r="D4" t="n">
-        <v>46.57116584635595</v>
+        <v>37.8414652601933</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.08489763311751</v>
+        <v>27.95526587842793</v>
       </c>
       <c r="C5" t="n">
-        <v>72.796592269901</v>
+        <v>107.3295677667826</v>
       </c>
       <c r="D5" t="n">
-        <v>35.80924751240241</v>
+        <v>31.58773238414113</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.68055644768807</v>
+        <v>21.05161602216436</v>
       </c>
       <c r="C6" t="n">
-        <v>63.79887456047898</v>
+        <v>124.3373649951543</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2881194078966</v>
+        <v>32.88560284915541</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.45641487148353</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>40.96244121199391</v>
+        <v>77.55315989697678</v>
       </c>
       <c r="D7" t="n">
         <v>33.29695513723482</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>24.45042657426681</v>
+        <v>32.46148784092078</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6213,7 +6213,7 @@
         <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286623067503333</v>
+        <v>7.264449546742279</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59871432534709</v>
+        <v>75.36866404745115</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375795184065416</v>
+        <v>5.448337160056709</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.391758391723482</v>
+        <v>4.975497365122835</v>
       </c>
       <c r="C2" t="n">
-        <v>3.451824928131785</v>
+        <v>5.293583621298801</v>
       </c>
       <c r="D2" t="n">
-        <v>40.55501591473149</v>
+        <v>18.0366688224224</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.4988920646734</v>
+        <v>17.86289947877071</v>
       </c>
       <c r="C3" t="n">
-        <v>28.59340188618835</v>
+        <v>14.29424657383356</v>
       </c>
       <c r="D3" t="n">
-        <v>69.51755493771664</v>
+        <v>52.33206137487623</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.9690924617454</v>
+        <v>32.23863111205676</v>
       </c>
       <c r="C4" t="n">
-        <v>92.12131408029519</v>
+        <v>53.75657729373835</v>
       </c>
       <c r="D4" t="n">
-        <v>62.14168443571036</v>
+        <v>52.08466095340604</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.08614142272902</v>
+        <v>33.84575210390879</v>
       </c>
       <c r="C5" t="n">
-        <v>101.2918193856647</v>
+        <v>107.2068493037517</v>
       </c>
       <c r="D5" t="n">
-        <v>44.17864669110647</v>
+        <v>38.11635461738242</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.34724525432967</v>
+        <v>29.94723197034471</v>
       </c>
       <c r="C6" t="n">
-        <v>92.41780188697776</v>
+        <v>148.4883585196258</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>35.34095385747668</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.0382724649324</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>68.57016840311847</v>
+        <v>133.3075937688574</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>41.0566889916016</v>
+        <v>70.18023463808323</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.84531013555227</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.495715081403003</v>
+        <v>7.469455900447919</v>
       </c>
       <c r="C21" t="n">
-        <v>85.26375905095917</v>
+        <v>84.03137888003909</v>
       </c>
       <c r="D21" t="n">
-        <v>7.495715081403003</v>
+        <v>6.535773912891929</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_45_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497629454084</v>
+        <v>10.84497641358025</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907181063455</v>
+        <v>37.78907222542465</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.813508993922111</v>
+        <v>6.156539853331748</v>
       </c>
       <c r="C2" t="n">
-        <v>6.848671984825748</v>
+        <v>13.15541923690726</v>
       </c>
       <c r="D2" t="n">
-        <v>14.61527807312227</v>
+        <v>31.83022406709009</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.32293824143497</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="C3" t="n">
-        <v>17.88253443285565</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D3" t="n">
-        <v>54.17774705886023</v>
+        <v>81.35743225093319</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.45108952680157</v>
+        <v>40.44506017185584</v>
       </c>
       <c r="C4" t="n">
-        <v>43.6740283711236</v>
+        <v>63.60939725355934</v>
       </c>
       <c r="D4" t="n">
-        <v>64.50278766442393</v>
+        <v>102.3187274843068</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.84070449666732</v>
+        <v>50.85453107998479</v>
       </c>
       <c r="C5" t="n">
-        <v>103.0589652533089</v>
+        <v>117.2697632722815</v>
       </c>
       <c r="D5" t="n">
-        <v>47.66385104118265</v>
+        <v>72.0602814917159</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>44.43782808502763</v>
       </c>
       <c r="C6" t="n">
-        <v>158.5915241440298</v>
+        <v>143.4569015353609</v>
       </c>
       <c r="D6" t="n">
-        <v>39.28561613314037</v>
+        <v>47.77871552257953</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>30.84160412891355</v>
       </c>
       <c r="C7" t="n">
-        <v>175.2881073501552</v>
+        <v>120.4319726276605</v>
       </c>
       <c r="D7" t="n">
-        <v>37.60879105428681</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.93590866178347</v>
+        <v>15.93867397844697</v>
       </c>
       <c r="C8" t="n">
-        <v>123.3369640845268</v>
+        <v>76.2719791429347</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>59.01874498850123</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.660762961016333</v>
+        <v>7.662728090391663</v>
       </c>
       <c r="C21" t="n">
-        <v>92.88675090232304</v>
+        <v>92.91057809599891</v>
       </c>
       <c r="D21" t="n">
-        <v>7.660762961016333</v>
+        <v>7.662728090391663</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.044620615047611</v>
+        <v>7.531968386981529</v>
       </c>
       <c r="C2" t="n">
-        <v>5.884595739255381</v>
+        <v>11.34016773175491</v>
       </c>
       <c r="D2" t="n">
-        <v>17.62924352515997</v>
+        <v>27.68823050287279</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.60135367881356</v>
+        <v>20.38599107868502</v>
       </c>
       <c r="C3" t="n">
-        <v>22.17768063893545</v>
+        <v>40.0602150717911</v>
       </c>
       <c r="D3" t="n">
-        <v>53.10273332270997</v>
+        <v>85.97655519941442</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.82571623919635</v>
+        <v>39.28365263773187</v>
       </c>
       <c r="C4" t="n">
-        <v>43.6612656509684</v>
+        <v>67.8976712257094</v>
       </c>
       <c r="D4" t="n">
-        <v>74.99374363200535</v>
+        <v>114.9921085984289</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>54.97787143782139</v>
       </c>
       <c r="C5" t="n">
-        <v>92.11247835095699</v>
+        <v>117.0979574240383</v>
       </c>
       <c r="D5" t="n">
-        <v>57.48132808365076</v>
+        <v>89.01997308257954</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.68562941712533</v>
+        <v>55.54728510628455</v>
       </c>
       <c r="C6" t="n">
-        <v>160.0808354113722</v>
+        <v>161.8116566139593</v>
       </c>
       <c r="D6" t="n">
-        <v>44.71958967614647</v>
+        <v>56.79508643838223</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.09355343600648</v>
+        <v>40.48334833232147</v>
       </c>
       <c r="C7" t="n">
-        <v>201.9376487819349</v>
+        <v>160.4362280803095</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.69524160552276</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="C8" t="n">
-        <v>172.9888542268092</v>
+        <v>113.1562403914873</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>11.42656152972862</v>
       </c>
       <c r="C9" t="n">
-        <v>102.1734288240783</v>
+        <v>65.67499442329461</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>38.72012945549421</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1251,7 +1251,7 @@
         <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.838115205283971</v>
+        <v>7.835133593973918</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9157332680311</v>
+        <v>100.8773450224142</v>
       </c>
       <c r="D21" t="n">
-        <v>8.817879605944468</v>
+        <v>8.814525293220658</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.239407571115979</v>
+        <v>10.48702897676443</v>
       </c>
       <c r="C2" t="n">
-        <v>8.154396431474007</v>
+        <v>9.006553438760239</v>
       </c>
       <c r="D2" t="n">
-        <v>23.76713017211103</v>
+        <v>27.88948878224339</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.95616551067416</v>
+        <v>21.96169614400115</v>
       </c>
       <c r="C3" t="n">
-        <v>22.3003991019663</v>
+        <v>41.49356671999144</v>
       </c>
       <c r="D3" t="n">
-        <v>53.90776644019236</v>
+        <v>86.7668621013331</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.86851222755571</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="C4" t="n">
-        <v>48.37070938824035</v>
+        <v>81.79627347473149</v>
       </c>
       <c r="D4" t="n">
-        <v>81.06879842588461</v>
+        <v>127.116692745877</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.55938487390499</v>
+        <v>56.03325021988672</v>
       </c>
       <c r="C5" t="n">
-        <v>85.85383673638358</v>
+        <v>118.9632780621073</v>
       </c>
       <c r="D5" t="n">
-        <v>68.20692175254716</v>
+        <v>103.206227408946</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.88438442173969</v>
+        <v>62.71207985187777</v>
       </c>
       <c r="C6" t="n">
-        <v>154.8883718036108</v>
+        <v>170.7072725621397</v>
       </c>
       <c r="D6" t="n">
-        <v>50.35482149852316</v>
+        <v>67.46177524502383</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.05847256056086</v>
+        <v>50.60418541540184</v>
       </c>
       <c r="C7" t="n">
-        <v>214.3940636534184</v>
+        <v>191.8168116988545</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>48.26860762699867</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.87181732356695</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="C8" t="n">
-        <v>215.3807200961865</v>
+        <v>153.0446496150353</v>
       </c>
       <c r="D8" t="n">
         <v>39.72151211382594</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.75468624712531</v>
+        <v>16.41874860582365</v>
       </c>
       <c r="C9" t="n">
-        <v>148.656237377052</v>
+        <v>95.62811687986479</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>78.43673283079892</v>
+        <v>54.6637121724624</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>43.35790561035613</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.001187999613997</v>
+        <v>7.991305500828474</v>
       </c>
       <c r="C21" t="n">
-        <v>109.0161864947407</v>
+        <v>107.8826242611844</v>
       </c>
       <c r="D21" t="n">
-        <v>10.0014849995175</v>
+        <v>9.989131876035593</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.563965150594174</v>
+        <v>9.409069997501431</v>
       </c>
       <c r="C2" t="n">
-        <v>5.544911033585985</v>
+        <v>6.268459091615885</v>
       </c>
       <c r="D2" t="n">
-        <v>19.42682357163588</v>
+        <v>23.14372037991431</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.91260875878881</v>
+        <v>26.10958019444392</v>
       </c>
       <c r="C3" t="n">
-        <v>33.80157345721769</v>
+        <v>57.80530482605219</v>
       </c>
       <c r="D3" t="n">
-        <v>59.25829142833748</v>
+        <v>94.14960483726912</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.36028571192535</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="C4" t="n">
-        <v>69.78655380868027</v>
+        <v>103.3525078168787</v>
       </c>
       <c r="D4" t="n">
-        <v>77.43142318165017</v>
+        <v>120.0716712202019</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.23153789394879</v>
+        <v>35.31837366027901</v>
       </c>
       <c r="C5" t="n">
-        <v>92.55426481786806</v>
+        <v>102.0035864712436</v>
       </c>
       <c r="D5" t="n">
-        <v>48.40016181936777</v>
+        <v>68.03511590430396</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.72709950041517</v>
+        <v>31.396291581813</v>
       </c>
       <c r="C6" t="n">
-        <v>141.2028088064103</v>
+        <v>126.3096961329861</v>
       </c>
       <c r="D6" t="n">
-        <v>28.09565580013523</v>
+        <v>31.75855648468008</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>151.4532365864512</v>
+        <v>107.6162380964226</v>
       </c>
       <c r="D7" t="n">
         <v>27.90716024091983</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>109.5679525324653</v>
+        <v>70.43058030266617</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>59.79530742256046</v>
+        <v>41.71249645803847</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.911282853719293</v>
+        <v>5.545892781290231</v>
       </c>
       <c r="C2" t="n">
-        <v>2.720422888467912</v>
+        <v>3.912264601423539</v>
       </c>
       <c r="D2" t="n">
-        <v>13.83282515283756</v>
+        <v>16.06531943229481</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.82072538521711</v>
+        <v>29.5800583289564</v>
       </c>
       <c r="C3" t="n">
-        <v>28.18106785040469</v>
+        <v>41.94517066394497</v>
       </c>
       <c r="D3" t="n">
-        <v>60.99598486485433</v>
+        <v>92.55917355638928</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.78368101436299</v>
+        <v>36.51414236405162</v>
       </c>
       <c r="C4" t="n">
-        <v>78.68216975686063</v>
+        <v>126.3509295365645</v>
       </c>
       <c r="D4" t="n">
-        <v>88.33078619419827</v>
+        <v>135.5273253281594</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.64311116620645</v>
+        <v>39.29445186247859</v>
       </c>
       <c r="C5" t="n">
-        <v>112.2628499806228</v>
+        <v>141.8625432636641</v>
       </c>
       <c r="D5" t="n">
-        <v>60.37748381117885</v>
+        <v>88.23457491918209</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.67805317293184</v>
+        <v>36.99127174831558</v>
       </c>
       <c r="C6" t="n">
-        <v>152.0707558924225</v>
+        <v>147.8040803697658</v>
       </c>
       <c r="D6" t="n">
-        <v>33.48937768726721</v>
+        <v>39.20511282139213</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>180.7976754663884</v>
+        <v>136.4216974867282</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24273802932299</v>
+        <v>30.42239785920016</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>142.36323459283</v>
+        <v>93.87962421860124</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>66.00780689503428</v>
+        <v>45.37343364717482</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>35.3036474447153</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>29.60951076008381</v>
@@ -2150,7 +2150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
         <v>29.14219885286231</v>
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.752239725631309</v>
+        <v>6.361725123519331</v>
       </c>
       <c r="C2" t="n">
-        <v>9.803732574608649</v>
+        <v>11.19290557611789</v>
       </c>
       <c r="D2" t="n">
-        <v>15.21316242500857</v>
+        <v>18.56190384419444</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.00034415736527</v>
+        <v>24.21480712524758</v>
       </c>
       <c r="C3" t="n">
-        <v>18.64338890364693</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="D3" t="n">
-        <v>58.55634181980101</v>
+        <v>84.67083075276616</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.2288546927433</v>
+        <v>45.80540263704343</v>
       </c>
       <c r="C4" t="n">
-        <v>74.3428449040897</v>
+        <v>116.6257367782956</v>
       </c>
       <c r="D4" t="n">
-        <v>96.25643541058277</v>
+        <v>148.5580626066273</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.9508401659922</v>
+        <v>45.7248993252952</v>
       </c>
       <c r="C5" t="n">
-        <v>129.737959116216</v>
+        <v>184.519481013188</v>
       </c>
       <c r="D5" t="n">
-        <v>76.40451508300804</v>
+        <v>112.0174130545611</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.39378830705677</v>
+        <v>44.39757642915352</v>
       </c>
       <c r="C6" t="n">
-        <v>165.0317890838888</v>
+        <v>183.0645309154943</v>
       </c>
       <c r="D6" t="n">
-        <v>43.06927178530758</v>
+        <v>53.85671555957153</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.75124228239384</v>
+        <v>28.86534600026472</v>
       </c>
       <c r="C7" t="n">
-        <v>202.5365148815255</v>
+        <v>172.832756341834</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>188.7606310955342</v>
+        <v>132.4328565643735</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>114.3765527878661</v>
+        <v>74.54999366968578</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>52.52841091572559</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2495,7 +2495,7 @@
         <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.201078352921349</v>
+        <v>3.84746925294325</v>
       </c>
       <c r="C2" t="n">
-        <v>4.524875168873549</v>
+        <v>5.385867905498002</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47524800431347</v>
+        <v>12.97477765932585</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.69109363052752</v>
+        <v>25.0247489812512</v>
       </c>
       <c r="C3" t="n">
-        <v>28.49522711576367</v>
+        <v>36.15776794741003</v>
       </c>
       <c r="D3" t="n">
-        <v>59.11102927270046</v>
+        <v>83.62036070922208</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.03214529899544</v>
+        <v>50.28511741152163</v>
       </c>
       <c r="C4" t="n">
-        <v>71.22874118621884</v>
+        <v>111.8907676007132</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6971012610693</v>
+        <v>157.9131364803952</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>47.19752088166541</v>
       </c>
       <c r="C5" t="n">
-        <v>153.5698846368073</v>
+        <v>220.7705149925015</v>
       </c>
       <c r="D5" t="n">
-        <v>82.54043823455059</v>
+        <v>118.2269672839222</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.51704654943536</v>
+        <v>35.54221213684728</v>
       </c>
       <c r="C6" t="n">
-        <v>208.5840807396859</v>
+        <v>217.1576834408733</v>
       </c>
       <c r="D6" t="n">
-        <v>42.78751019418875</v>
+        <v>52.5284109157256</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.204465564390594</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>225.2335400560075</v>
+        <v>176.9649324290088</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>143.4480658060227</v>
+        <v>93.87962421860124</v>
       </c>
       <c r="D8" t="n">
         <v>31.29320807286708</v>
@@ -2747,7 +2747,7 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
         <v>31.61718481526852</v>
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.980586030093316</v>
+        <v>4.381540004053514</v>
       </c>
       <c r="C2" t="n">
-        <v>8.17206789015045</v>
+        <v>4.077198215737003</v>
       </c>
       <c r="D2" t="n">
-        <v>15.1905822278109</v>
+        <v>17.31115726898401</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.73817646260236</v>
+        <v>19.21771131063132</v>
       </c>
       <c r="C3" t="n">
-        <v>22.81581664669588</v>
+        <v>28.73575530330414</v>
       </c>
       <c r="D3" t="n">
-        <v>54.22192570555134</v>
+        <v>75.73201790559895</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.68831261833081</v>
+        <v>49.3406761200362</v>
       </c>
       <c r="C4" t="n">
-        <v>71.82858903351364</v>
+        <v>101.4891506742183</v>
       </c>
       <c r="D4" t="n">
-        <v>108.7000875619111</v>
+        <v>162.2396986130109</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.84823968313181</v>
+        <v>58.53670686571608</v>
       </c>
       <c r="C5" t="n">
-        <v>144.1941940612503</v>
+        <v>215.8617764712675</v>
       </c>
       <c r="D5" t="n">
-        <v>97.9784208838317</v>
+        <v>141.3225820263284</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.13719230334986</v>
+        <v>45.72588107299945</v>
       </c>
       <c r="C6" t="n">
-        <v>227.3413523770254</v>
+        <v>275.7640943935908</v>
       </c>
       <c r="D6" t="n">
-        <v>55.94980166502573</v>
+        <v>71.32593420893927</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="C7" t="n">
-        <v>264.5790427991069</v>
+        <v>236.1927896785146</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>209.6227698107789</v>
+        <v>148.0377363233765</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>91.30155474724909</v>
+        <v>60.4609323660398</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>35.01894061048373</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
+        <v>23.10052348092744</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.98900515327081</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.97920337176157</v>
+        <v>3.005129722699487</v>
       </c>
       <c r="C2" t="n">
-        <v>3.986877426946297</v>
+        <v>3.328124717396687</v>
       </c>
       <c r="D2" t="n">
-        <v>11.8811107167949</v>
+        <v>13.08276990679299</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.77606371244049</v>
+        <v>17.56837516749667</v>
       </c>
       <c r="C3" t="n">
-        <v>27.29749491658256</v>
+        <v>23.56194490192345</v>
       </c>
       <c r="D3" t="n">
-        <v>53.87831400906496</v>
+        <v>72.94385442553801</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.14478424307656</v>
+        <v>45.12897846881738</v>
       </c>
       <c r="C4" t="n">
-        <v>67.11914529624168</v>
+        <v>91.03648286710248</v>
       </c>
       <c r="D4" t="n">
-        <v>110.7676482270549</v>
+        <v>163.1841399044963</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.41336650787948</v>
+        <v>65.11441648416971</v>
       </c>
       <c r="C5" t="n">
-        <v>144.439630987312</v>
+        <v>212.4992905842222</v>
       </c>
       <c r="D5" t="n">
-        <v>109.6612185643687</v>
+        <v>157.7423123798563</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.98626519880311</v>
+        <v>53.17243740971151</v>
       </c>
       <c r="C6" t="n">
-        <v>239.7791140421282</v>
+        <v>310.0182535424664</v>
       </c>
       <c r="D6" t="n">
-        <v>65.40894079544375</v>
+        <v>84.16621243278331</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>301.3494213139669</v>
+        <v>291.5280172806819</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>43.5375654402333</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>257.1884460815369</v>
+        <v>188.5102854309513</v>
       </c>
       <c r="D8" t="n">
-        <v>34.88149593188918</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>107.8312408436526</v>
+        <v>66.89530681967339</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>35.16129402759952</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.988440011727291</v>
+        <v>3.979023445312322</v>
       </c>
       <c r="C2" t="n">
-        <v>8.737554567796613</v>
+        <v>10.44481382548181</v>
       </c>
       <c r="D2" t="n">
-        <v>13.04448174632737</v>
+        <v>14.56520894020568</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.326603190344699</v>
+        <v>14.08317081742049</v>
       </c>
       <c r="C3" t="n">
-        <v>21.48554850744145</v>
+        <v>18.70720250442297</v>
       </c>
       <c r="D3" t="n">
-        <v>51.56629816556372</v>
+        <v>67.54424205218055</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.00140802052752</v>
+        <v>39.37299167881833</v>
       </c>
       <c r="C4" t="n">
-        <v>67.41268785981148</v>
+        <v>77.12511789792518</v>
       </c>
       <c r="D4" t="n">
-        <v>110.5506819844163</v>
+        <v>161.7802406874234</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.18618187757097</v>
+        <v>66.3661448070844</v>
       </c>
       <c r="C5" t="n">
-        <v>134.9412219487241</v>
+        <v>193.6988220478957</v>
       </c>
       <c r="D5" t="n">
-        <v>121.1967540892688</v>
+        <v>170.8977316167635</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.48565598509524</v>
+        <v>64.44290105446488</v>
       </c>
       <c r="C6" t="n">
-        <v>238.8130743011494</v>
+        <v>321.5704787783386</v>
       </c>
       <c r="D6" t="n">
-        <v>79.89953691012668</v>
+        <v>104.8555635520806</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.68001666834032</v>
       </c>
       <c r="C7" t="n">
-        <v>322.3696214095954</v>
+        <v>351.2349674098601</v>
       </c>
       <c r="D7" t="n">
-        <v>47.60985491744906</v>
+        <v>52.64033015400972</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>318.6065824592173</v>
+        <v>262.7794992572225</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>185.7093592307351</v>
+        <v>122.5859270907779</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>68.18728679846222</v>
+        <v>46.54956739686252</v>
       </c>
       <c r="D10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.293583621298801</v>
+        <v>6.957645979997145</v>
       </c>
       <c r="C2" t="n">
-        <v>14.07335334037803</v>
+        <v>6.972372195560848</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3719435111893</v>
+        <v>10.29362467902781</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.114684554947629</v>
+        <v>2.909900195387546</v>
       </c>
       <c r="C2" t="n">
-        <v>4.893030557966103</v>
+        <v>6.183047041346412</v>
       </c>
       <c r="D2" t="n">
-        <v>9.600510799829559</v>
+        <v>10.83653115947629</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.772537632251</v>
+        <v>18.46176557836127</v>
       </c>
       <c r="C3" t="n">
-        <v>28.63267179435823</v>
+        <v>27.66565030567511</v>
       </c>
       <c r="D3" t="n">
-        <v>56.53394154905258</v>
+        <v>73.69489141928682</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.55166976099125</v>
+        <v>52.02084735262999</v>
       </c>
       <c r="C4" t="n">
-        <v>92.03197503920875</v>
+        <v>110.8697499882965</v>
       </c>
       <c r="D4" t="n">
-        <v>113.2180904968549</v>
+        <v>164.205157516913</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.90113088597411</v>
+        <v>36.91371367968008</v>
       </c>
       <c r="C5" t="n">
-        <v>202.1173086118121</v>
+        <v>278.4236489243955</v>
       </c>
       <c r="D5" t="n">
-        <v>112.287393673229</v>
+        <v>154.9934188079652</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.28054316370311</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>261.4747565582786</v>
+        <v>288.0408494351972</v>
       </c>
       <c r="D6" t="n">
-        <v>66.41523219229674</v>
+        <v>80.82532499523143</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>224.0358078568264</v>
+        <v>184.810078333645</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>136.8556299720053</v>
+        <v>90.29133635957915</v>
       </c>
       <c r="D8" t="n">
-        <v>24.61732368398877</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>20.63437324785945</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.776546738526</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.318528224532471</v>
+        <v>6.706318567709961</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82573193472958</v>
+        <v>8.224100518475531</v>
       </c>
       <c r="D2" t="n">
-        <v>9.192103754862885</v>
+        <v>13.15443748920301</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.24591995214721</v>
+        <v>14.7753029489145</v>
       </c>
       <c r="C3" t="n">
-        <v>35.46072707739479</v>
+        <v>17.56837516749667</v>
       </c>
       <c r="D3" t="n">
-        <v>9.326603190344699</v>
+        <v>11.78097245096173</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39741204648255</v>
+        <v>13.39784340465342</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13939247864393</v>
+        <v>70.14165076553849</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576166123115594</v>
+        <v>1.576216871135696</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.777184328864979</v>
+        <v>4.73398742987812</v>
       </c>
       <c r="C2" t="n">
-        <v>9.078221021170256</v>
+        <v>5.572399969304896</v>
       </c>
       <c r="D2" t="n">
-        <v>10.18366893615216</v>
+        <v>28.71219335840221</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.58310138306037</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="C3" t="n">
-        <v>39.68715094417731</v>
+        <v>26.6397239547372</v>
       </c>
       <c r="D3" t="n">
-        <v>14.7900291644782</v>
+        <v>19.98347451994383</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.13283903970958</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C4" t="n">
-        <v>54.57339138367169</v>
+        <v>27.32498385230147</v>
       </c>
       <c r="D4" t="n">
-        <v>19.96089432274615</v>
+        <v>21.24992905842221</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43790382913611</v>
+        <v>15.4403255290097</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12725294149621</v>
+        <v>86.14076347763304</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250085016660234</v>
+        <v>3.250594848212568</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.771293842639499</v>
+        <v>5.751078051477815</v>
       </c>
       <c r="C2" t="n">
-        <v>4.18911745402114</v>
+        <v>10.16796097288421</v>
       </c>
       <c r="D2" t="n">
-        <v>13.15247399379452</v>
+        <v>28.86141900944773</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15113239319178</v>
+        <v>17.89726064841935</v>
       </c>
       <c r="C3" t="n">
-        <v>37.06097583531709</v>
+        <v>23.89083038284613</v>
       </c>
       <c r="D3" t="n">
-        <v>19.50241814486289</v>
+        <v>38.31270415823177</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.61928717939726</v>
+        <v>29.26491731589317</v>
       </c>
       <c r="C4" t="n">
-        <v>79.97120449253669</v>
+        <v>49.83842220608933</v>
       </c>
       <c r="D4" t="n">
-        <v>22.89631995844411</v>
+        <v>26.49540704221292</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.65825398793088</v>
+        <v>14.70167187109599</v>
       </c>
       <c r="C5" t="n">
-        <v>59.78843518863076</v>
+        <v>31.07231483941155</v>
       </c>
       <c r="D5" t="n">
-        <v>29.84513020910304</v>
+        <v>30.31146036862028</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
         <v>12.23650338573225</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72575625013592</v>
+        <v>16.73069436440616</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0271131258291</v>
+        <v>102.0572356228776</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181439062533979</v>
+        <v>4.18267359110154</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.390375733391736</v>
+        <v>7.319910882864218</v>
       </c>
       <c r="C2" t="n">
-        <v>5.732424845097126</v>
+        <v>7.80882123957913</v>
       </c>
       <c r="D2" t="n">
-        <v>15.620587722271</v>
+        <v>30.90738122509809</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.66516727958961</v>
+        <v>18.81519475189012</v>
       </c>
       <c r="C3" t="n">
-        <v>25.2260072606218</v>
+        <v>33.09471511015998</v>
       </c>
       <c r="D3" t="n">
-        <v>25.15728492132452</v>
+        <v>51.72337779824321</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.21386643527233</v>
+        <v>31.94508854848696</v>
       </c>
       <c r="C4" t="n">
-        <v>86.95241241743575</v>
+        <v>54.80312034646545</v>
       </c>
       <c r="D4" t="n">
-        <v>27.26117025152543</v>
+        <v>39.01563551447249</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.88101290580367</v>
+        <v>29.30516897176729</v>
       </c>
       <c r="C5" t="n">
-        <v>105.7833151325938</v>
+        <v>63.98540662428588</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09685853201772</v>
+        <v>32.64311116620645</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>12.7597749120958</v>
       </c>
       <c r="C6" t="n">
-        <v>54.94351026817275</v>
+        <v>31.27553661419064</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04159931834449</v>
+        <v>18.05051685944487</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6999574577712</v>
+        <v>117.7581337973308</v>
       </c>
       <c r="D21" t="n">
-        <v>6.013866439448162</v>
+        <v>6.016838953148287</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.627778751370216</v>
+        <v>7.496625469628643</v>
       </c>
       <c r="C2" t="n">
-        <v>4.920519493685013</v>
+        <v>6.742643232767094</v>
       </c>
       <c r="D2" t="n">
-        <v>27.34756404949915</v>
+        <v>26.05951106152733</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.95063487734718</v>
+        <v>19.73803759388213</v>
       </c>
       <c r="C3" t="n">
-        <v>22.08932334555324</v>
+        <v>29.57514959043516</v>
       </c>
       <c r="D3" t="n">
-        <v>29.57024085191393</v>
+        <v>59.93569734426777</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.21989579021806</v>
+        <v>24.75967710110456</v>
       </c>
       <c r="C4" t="n">
-        <v>61.65670106981243</v>
+        <v>58.26181750852697</v>
       </c>
       <c r="D4" t="n">
-        <v>29.09900195387546</v>
+        <v>48.21755674637784</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.73942025221387</v>
+        <v>23.53740120931728</v>
       </c>
       <c r="C5" t="n">
-        <v>99.20560551414022</v>
+        <v>62.39006660488482</v>
       </c>
       <c r="D5" t="n">
-        <v>27.16986771503048</v>
+        <v>31.29320807286709</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="C6" t="n">
-        <v>76.43789450495242</v>
+        <v>45.56487444950297</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>31.11452999069417</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>31.85967649821749</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>18.99190933865455</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.046665722599699</v>
+        <v>7.051459886523507</v>
       </c>
       <c r="C21" t="n">
-        <v>66.06249114937218</v>
+        <v>66.10743643615787</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404166076624812</v>
+        <v>4.407162429077192</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.808600255400877</v>
+        <v>5.654866776461628</v>
       </c>
       <c r="C2" t="n">
-        <v>2.64090132442392</v>
+        <v>5.43593703841459</v>
       </c>
       <c r="D2" t="n">
-        <v>21.83505069015331</v>
+        <v>30.47835747834223</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.48769192929919</v>
+        <v>23.66502841086936</v>
       </c>
       <c r="C3" t="n">
-        <v>20.25836387713293</v>
+        <v>27.50857067299563</v>
       </c>
       <c r="D3" t="n">
-        <v>45.39601384437251</v>
+        <v>67.34298377280996</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.52544031041707</v>
+        <v>33.27241144462865</v>
       </c>
       <c r="C4" t="n">
-        <v>57.85341046356029</v>
+        <v>68.14016290865837</v>
       </c>
       <c r="D4" t="n">
-        <v>37.8414652601933</v>
+        <v>68.44646819238336</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.95526587842793</v>
+        <v>31.3668391506856</v>
       </c>
       <c r="C5" t="n">
-        <v>107.3295677667826</v>
+        <v>89.06906046779189</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58773238414113</v>
+        <v>41.82245220091413</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.05161602216436</v>
+        <v>24.47300677146449</v>
       </c>
       <c r="C6" t="n">
-        <v>124.3373649951543</v>
+        <v>77.12217265481245</v>
       </c>
       <c r="D6" t="n">
-        <v>32.88560284915541</v>
+        <v>34.5359207399943</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>77.55315989697678</v>
+        <v>47.19064864773568</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>32.46148784092078</v>
+        <v>24.45042657426681</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>21.07321447165778</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.264449546742279</v>
+        <v>7.269745845789823</v>
       </c>
       <c r="C21" t="n">
-        <v>75.36866404745115</v>
+        <v>75.42361315006941</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448337160056709</v>
+        <v>5.452309384342366</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.975497365122835</v>
+        <v>5.927792638242241</v>
       </c>
       <c r="C2" t="n">
-        <v>5.293583621298801</v>
+        <v>8.947648576505429</v>
       </c>
       <c r="D2" t="n">
-        <v>18.0366688224224</v>
+        <v>29.08623923372025</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86289947877071</v>
+        <v>21.33828635180442</v>
       </c>
       <c r="C3" t="n">
-        <v>14.29424657383356</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D3" t="n">
-        <v>52.33206137487623</v>
+        <v>76.7481267794944</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.23863111205676</v>
+        <v>40.47058561216627</v>
       </c>
       <c r="C4" t="n">
-        <v>53.75657729373835</v>
+        <v>68.59962083424587</v>
       </c>
       <c r="D4" t="n">
-        <v>52.08466095340604</v>
+        <v>85.15286887555135</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.84575210390879</v>
+        <v>41.01251034491051</v>
       </c>
       <c r="C5" t="n">
-        <v>107.2068493037517</v>
+        <v>109.7593933347934</v>
       </c>
       <c r="D5" t="n">
-        <v>38.11635461738242</v>
+        <v>56.91682315370885</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.94723197034471</v>
+        <v>34.25415914887547</v>
       </c>
       <c r="C6" t="n">
-        <v>148.4883585196258</v>
+        <v>111.9801066417997</v>
       </c>
       <c r="D6" t="n">
-        <v>35.34095385747668</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>133.3075937688574</v>
+        <v>81.08646988456105</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>70.18023463808323</v>
+        <v>45.06221962492859</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
         <v>26.29905750136355</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.469455900447919</v>
+        <v>7.473845597719437</v>
       </c>
       <c r="C21" t="n">
-        <v>84.03137888003909</v>
+        <v>84.08076297434367</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535773912891929</v>
+        <v>6.539614898004507</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_45_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_45_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641358025</v>
+        <v>10.84497654307962</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907222542465</v>
+        <v>37.78907267666222</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.156539853331748</v>
+        <v>0.8609927366244527</v>
       </c>
       <c r="C2" t="n">
-        <v>13.15541923690726</v>
+        <v>3.298672286269283</v>
       </c>
       <c r="D2" t="n">
-        <v>31.83022406709009</v>
+        <v>14.37573163328604</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.61179305066178</v>
+        <v>8.128870991163589</v>
       </c>
       <c r="C3" t="n">
-        <v>29.65859814529614</v>
+        <v>37.38986131623977</v>
       </c>
       <c r="D3" t="n">
-        <v>81.35743225093319</v>
+        <v>68.25110039923827</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.44506017185584</v>
+        <v>16.47667172037422</v>
       </c>
       <c r="C4" t="n">
-        <v>63.60939725355934</v>
+        <v>117.3276863868321</v>
       </c>
       <c r="D4" t="n">
-        <v>102.3187274843068</v>
+        <v>82.38335860187109</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.85453107998479</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="C5" t="n">
-        <v>117.2697632722815</v>
+        <v>149.8637870532756</v>
       </c>
       <c r="D5" t="n">
-        <v>72.0602814917159</v>
+        <v>49.89732706834415</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.43782808502763</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>143.4569015353609</v>
+        <v>105.0165701755771</v>
       </c>
       <c r="D6" t="n">
-        <v>47.77871552257953</v>
+        <v>29.90698031447059</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.84160412891355</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>120.4319726276605</v>
+        <v>48.74770050667112</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>76.2719791429347</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>41.82343394861835</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.43894870145212</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.662728090391663</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.91057809599891</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.662728090391663</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.531968386981529</v>
+        <v>0.8403760348352697</v>
       </c>
       <c r="C2" t="n">
-        <v>11.34016773175491</v>
+        <v>10.16599747747572</v>
       </c>
       <c r="D2" t="n">
-        <v>27.68823050287279</v>
+        <v>13.74544960715959</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.38599107868502</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C3" t="n">
-        <v>40.0602150717911</v>
+        <v>23.53740120931728</v>
       </c>
       <c r="D3" t="n">
-        <v>85.97655519941442</v>
+        <v>63.99522410132834</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.28365263773187</v>
+        <v>16.23418003742526</v>
       </c>
       <c r="C4" t="n">
-        <v>67.8976712257094</v>
+        <v>104.2586609478985</v>
       </c>
       <c r="D4" t="n">
-        <v>114.9921085984289</v>
+        <v>97.21363942222341</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.97787143782139</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="C5" t="n">
-        <v>117.0979574240383</v>
+        <v>186.7284133477434</v>
       </c>
       <c r="D5" t="n">
-        <v>89.01997308257954</v>
+        <v>67.12699927787567</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.54728510628455</v>
+        <v>17.06670209062656</v>
       </c>
       <c r="C6" t="n">
-        <v>161.8116566139593</v>
+        <v>172.4783454206009</v>
       </c>
       <c r="D6" t="n">
-        <v>56.79508643838223</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.48334833232147</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>160.4362280803095</v>
+        <v>98.69313321252335</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>31.62013005838127</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.61594102565702</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>113.1562403914873</v>
+        <v>45.8132566186774</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>37.86600895279948</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.835133593973918</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8773450224142</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.814525293220658</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.48702897676443</v>
+        <v>0.45553093477052</v>
       </c>
       <c r="C2" t="n">
-        <v>9.006553438760239</v>
+        <v>4.328525628024187</v>
       </c>
       <c r="D2" t="n">
-        <v>27.88948878224339</v>
+        <v>9.383544557191014</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.96169614400115</v>
+        <v>4.918555998276521</v>
       </c>
       <c r="C3" t="n">
-        <v>41.49356671999144</v>
+        <v>32.89345683078938</v>
       </c>
       <c r="D3" t="n">
-        <v>86.7668621013331</v>
+        <v>62.92021036517807</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.00738062221102</v>
+        <v>17.56150293356694</v>
       </c>
       <c r="C4" t="n">
-        <v>81.79627347473149</v>
+        <v>96.97114773927444</v>
       </c>
       <c r="D4" t="n">
-        <v>127.116692745877</v>
+        <v>106.2241198518006</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.03325021988672</v>
+        <v>21.13211933391259</v>
       </c>
       <c r="C5" t="n">
-        <v>118.9632780621073</v>
+        <v>215.2236404635071</v>
       </c>
       <c r="D5" t="n">
-        <v>103.206227408946</v>
+        <v>75.69274799742909</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.71207985187777</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>170.7072725621397</v>
+        <v>210.9589284362589</v>
       </c>
       <c r="D6" t="n">
-        <v>67.46177524502383</v>
+        <v>38.7220929509027</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.60418541540184</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>191.8168116988545</v>
+        <v>89.88980154854221</v>
       </c>
       <c r="D7" t="n">
-        <v>48.26860762699867</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.71045084717197</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>153.0446496150353</v>
+        <v>40.3056519978528</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.41874860582365</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>95.62811687986479</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>54.6637121724624</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.991305500828474</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8826242611844</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.989131876035593</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.409069997501431</v>
+        <v>0.8315403054970485</v>
       </c>
       <c r="C2" t="n">
-        <v>6.268459091615885</v>
+        <v>9.670214886831081</v>
       </c>
       <c r="D2" t="n">
-        <v>23.14372037991431</v>
+        <v>14.06255411563131</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.10958019444392</v>
+        <v>3.229949946972006</v>
       </c>
       <c r="C3" t="n">
-        <v>57.80530482605219</v>
+        <v>24.19026343264141</v>
       </c>
       <c r="D3" t="n">
-        <v>94.14960483726912</v>
+        <v>56.28359588446964</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.9165768073348</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C4" t="n">
-        <v>103.3525078168787</v>
+        <v>90.05375341515142</v>
       </c>
       <c r="D4" t="n">
-        <v>120.0716712202019</v>
+        <v>112.8990224929747</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.31837366027901</v>
+        <v>24.1019061392592</v>
       </c>
       <c r="C5" t="n">
-        <v>102.0035864712436</v>
+        <v>199.0002596508285</v>
       </c>
       <c r="D5" t="n">
-        <v>68.03511590430396</v>
+        <v>95.08226515630359</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.396291581813</v>
+        <v>19.56230475482195</v>
       </c>
       <c r="C6" t="n">
-        <v>126.3096961329861</v>
+        <v>277.0923990374368</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75855648468008</v>
+        <v>50.47557646614552</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>107.6162380964226</v>
+        <v>185.1095113834403</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>70.43058030266617</v>
+        <v>74.76990515543707</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71249645803847</v>
+        <v>36.0546844384641</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.91689560250429</v>
-      </c>
-      <c r="D15" t="n">
-        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.545892781290231</v>
+        <v>0.5340707511102649</v>
       </c>
       <c r="C2" t="n">
-        <v>3.912264601423539</v>
+        <v>6.250787632939441</v>
       </c>
       <c r="D2" t="n">
-        <v>16.06531943229481</v>
+        <v>10.09334814736146</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.5800583289564</v>
+        <v>3.107231483941155</v>
       </c>
       <c r="C3" t="n">
-        <v>41.94517066394497</v>
+        <v>31.10667600906019</v>
       </c>
       <c r="D3" t="n">
-        <v>92.55917355638928</v>
+        <v>54.92387531408781</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.51414236405162</v>
+        <v>11.10356653503143</v>
       </c>
       <c r="C4" t="n">
-        <v>126.3509295365645</v>
+        <v>78.77150879794708</v>
       </c>
       <c r="D4" t="n">
-        <v>135.5273253281594</v>
+        <v>115.36222748293</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.29445186247859</v>
+        <v>24.51914891356409</v>
       </c>
       <c r="C5" t="n">
-        <v>141.8625432636641</v>
+        <v>192.3243752619502</v>
       </c>
       <c r="D5" t="n">
-        <v>88.23457491918209</v>
+        <v>109.2439757900639</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>23.30570875111504</v>
       </c>
       <c r="C6" t="n">
-        <v>147.8040803697658</v>
+        <v>305.1478031816979</v>
       </c>
       <c r="D6" t="n">
-        <v>39.20511282139213</v>
+        <v>61.46427851978007</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>136.4216974867282</v>
+        <v>260.0276604422187</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>116.6610796956485</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>45.37343364717482</v>
+        <v>45.92812110007426</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>40.15937158992001</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.361725123519331</v>
+        <v>0.4751658888554562</v>
       </c>
       <c r="C2" t="n">
-        <v>11.19290557611789</v>
+        <v>7.746971134211581</v>
       </c>
       <c r="D2" t="n">
-        <v>18.56190384419444</v>
+        <v>14.82242683871834</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.21480712524758</v>
+        <v>2.469095476180728</v>
       </c>
       <c r="C3" t="n">
-        <v>27.95526587842792</v>
+        <v>27.82763867687584</v>
       </c>
       <c r="D3" t="n">
-        <v>84.67083075276616</v>
+        <v>50.74653883251763</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.80540263704343</v>
+        <v>8.729700586162638</v>
       </c>
       <c r="C4" t="n">
-        <v>116.6257367782956</v>
+        <v>78.08232190956581</v>
       </c>
       <c r="D4" t="n">
-        <v>148.5580626066273</v>
+        <v>116.0641770914664</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.7248993252952</v>
+        <v>21.72116795646068</v>
       </c>
       <c r="C5" t="n">
-        <v>184.519481013188</v>
+        <v>170.676838383308</v>
       </c>
       <c r="D5" t="n">
-        <v>112.0174130545611</v>
+        <v>122.1294144083032</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.39757642915352</v>
+        <v>27.08936440328224</v>
       </c>
       <c r="C6" t="n">
-        <v>183.0645309154943</v>
+        <v>306.6371144490403</v>
       </c>
       <c r="D6" t="n">
-        <v>53.85671555957153</v>
+        <v>76.47814616082654</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.86534600026472</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>172.832756341834</v>
+        <v>340.3954910072711</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>45.99291644855457</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>132.4328565643735</v>
+        <v>209.2055270364741</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>40.63944621729671</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>74.54999366968578</v>
+        <v>83.75780538781659</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>40.42837046088366</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.84746925294325</v>
+        <v>0.3298672286269283</v>
       </c>
       <c r="C2" t="n">
-        <v>5.385867905498002</v>
+        <v>4.21366114662731</v>
       </c>
       <c r="D2" t="n">
-        <v>12.97477765932585</v>
+        <v>10.79038901737669</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.0247489812512</v>
+        <v>3.347759671481623</v>
       </c>
       <c r="C3" t="n">
-        <v>36.15776794741003</v>
+        <v>32.88854809226815</v>
       </c>
       <c r="D3" t="n">
-        <v>83.62036070922208</v>
+        <v>56.62229884243479</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.28511741152163</v>
+        <v>14.74094177926586</v>
       </c>
       <c r="C4" t="n">
-        <v>111.8907676007132</v>
+        <v>110.2316139805361</v>
       </c>
       <c r="D4" t="n">
-        <v>157.9131364803952</v>
+        <v>119.3569588915102</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.19752088166541</v>
+        <v>16.24792450528471</v>
       </c>
       <c r="C5" t="n">
-        <v>220.7705149925015</v>
+        <v>257.6105975943631</v>
       </c>
       <c r="D5" t="n">
-        <v>118.2269672839222</v>
+        <v>111.4774518172253</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.54221213684728</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>217.1576834408733</v>
+        <v>290.2949421641479</v>
       </c>
       <c r="D6" t="n">
-        <v>52.5284109157256</v>
+        <v>64.24164277509429</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>176.9649324290088</v>
+        <v>147.0815140594401</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>61.66848204226339</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>33.32542582065798</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.381540004053514</v>
+        <v>0.1904590546238812</v>
       </c>
       <c r="C2" t="n">
-        <v>4.077198215737003</v>
+        <v>3.945644023367931</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31115726898401</v>
+        <v>7.920740477863266</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.21771131063132</v>
+        <v>2.25311098124643</v>
       </c>
       <c r="C3" t="n">
-        <v>28.73575530330414</v>
+        <v>24.44551783574558</v>
       </c>
       <c r="D3" t="n">
-        <v>75.73201790559895</v>
+        <v>52.27806525114266</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.3406761200362</v>
+        <v>10.04426076214912</v>
       </c>
       <c r="C4" t="n">
-        <v>101.4891506742183</v>
+        <v>92.12131408029519</v>
       </c>
       <c r="D4" t="n">
-        <v>162.2396986130109</v>
+        <v>115.2601257216883</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.53670686571608</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="C5" t="n">
-        <v>215.8617764712675</v>
+        <v>209.8731154753619</v>
       </c>
       <c r="D5" t="n">
-        <v>141.3225820263284</v>
+        <v>113.588209381356</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.72588107299945</v>
+        <v>9.378635818669782</v>
       </c>
       <c r="C6" t="n">
-        <v>275.7640943935908</v>
+        <v>282.0836043658276</v>
       </c>
       <c r="D6" t="n">
-        <v>71.32593420893927</v>
+        <v>68.0252984272615</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>3.173990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>236.1927896785146</v>
+        <v>189.0021410307789</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>148.0377363233765</v>
+        <v>73.26783116793945</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>26.11939767148639</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4609323660398</v>
+        <v>28.95468504135117</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.005129722699487</v>
+        <v>0.2474004214701962</v>
       </c>
       <c r="C2" t="n">
-        <v>3.328124717396687</v>
+        <v>16.20767284941059</v>
       </c>
       <c r="D2" t="n">
-        <v>13.08276990679299</v>
+        <v>10.33583983031042</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.56837516749667</v>
+        <v>1.384264262988003</v>
       </c>
       <c r="C3" t="n">
-        <v>23.56194490192345</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="D3" t="n">
-        <v>72.94385442553801</v>
+        <v>46.66737712137213</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.12897846881738</v>
+        <v>7.172648727227196</v>
       </c>
       <c r="C4" t="n">
-        <v>91.03648286710248</v>
+        <v>75.73398140100744</v>
       </c>
       <c r="D4" t="n">
-        <v>163.1841399044963</v>
+        <v>115.5153801247924</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.11441648416971</v>
+        <v>15.41343895667493</v>
       </c>
       <c r="C5" t="n">
-        <v>212.4992905842222</v>
+        <v>188.839170911874</v>
       </c>
       <c r="D5" t="n">
-        <v>157.7423123798563</v>
+        <v>128.8052987971815</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.17243740971151</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="C6" t="n">
-        <v>310.0182535424664</v>
+        <v>309.4949820161028</v>
       </c>
       <c r="D6" t="n">
-        <v>84.16621243278331</v>
+        <v>86.38005350585986</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>291.5280172806819</v>
+        <v>301.5290811438441</v>
       </c>
       <c r="D7" t="n">
-        <v>43.5375654402333</v>
+        <v>44.13643153982385</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>188.5102854309513</v>
+        <v>159.6370854490526</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>66.89530681967339</v>
+        <v>58.02030757328223</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.2984356065578</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.979023445312322</v>
+        <v>0.2974695543867835</v>
       </c>
       <c r="C2" t="n">
-        <v>10.44481382548181</v>
+        <v>12.4642688531175</v>
       </c>
       <c r="D2" t="n">
-        <v>14.56520894020568</v>
+        <v>10.16501572977148</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.08317081742049</v>
+        <v>1.099557428756428</v>
       </c>
       <c r="C3" t="n">
-        <v>18.70720250442297</v>
+        <v>41.61137644450106</v>
       </c>
       <c r="D3" t="n">
-        <v>67.54424205218055</v>
+        <v>44.20809912223388</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.37299167881833</v>
+        <v>4.951935420220911</v>
       </c>
       <c r="C4" t="n">
-        <v>77.12511789792518</v>
+        <v>60.99303962174159</v>
       </c>
       <c r="D4" t="n">
-        <v>161.7802406874234</v>
+        <v>112.9500733735955</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.3661448070844</v>
+        <v>13.52357462599982</v>
       </c>
       <c r="C5" t="n">
-        <v>193.6988220478957</v>
+        <v>164.5900026169778</v>
       </c>
       <c r="D5" t="n">
-        <v>170.8977316167635</v>
+        <v>137.9846398318892</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.44290105446488</v>
+        <v>17.34846368174539</v>
       </c>
       <c r="C6" t="n">
-        <v>321.5704787783386</v>
+        <v>306.516359481418</v>
       </c>
       <c r="D6" t="n">
-        <v>104.8555635520806</v>
+        <v>104.3725436815912</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.68001666834032</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>351.2349674098601</v>
+        <v>371.4766415760208</v>
       </c>
       <c r="D7" t="n">
-        <v>52.64033015400972</v>
+        <v>55.63466065196249</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>262.7794992572225</v>
+        <v>269.2884865363789</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>122.5859270907779</v>
+        <v>119.3687398639611</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>24.18437294641592</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>46.54956739686252</v>
+        <v>44.27191272300992</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.957645979997145</v>
+        <v>4.773257338047992</v>
       </c>
       <c r="C2" t="n">
-        <v>6.972372195560848</v>
+        <v>11.58854990092935</v>
       </c>
       <c r="D2" t="n">
-        <v>10.29362467902781</v>
+        <v>13.17407244328795</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.909900195387546</v>
+        <v>0.3936808294029709</v>
       </c>
       <c r="C2" t="n">
-        <v>6.183047041346412</v>
+        <v>12.83831472843554</v>
       </c>
       <c r="D2" t="n">
-        <v>10.83653115947629</v>
+        <v>14.23043297305752</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.46176557836127</v>
+        <v>1.040652566501619</v>
       </c>
       <c r="C3" t="n">
-        <v>27.66565030567511</v>
+        <v>44.40444866308323</v>
       </c>
       <c r="D3" t="n">
-        <v>73.69489141928682</v>
+        <v>42.17097263592174</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.02084735262999</v>
+        <v>3.599087083768806</v>
       </c>
       <c r="C4" t="n">
-        <v>110.8697499882965</v>
+        <v>80.11159441424397</v>
       </c>
       <c r="D4" t="n">
-        <v>164.205157516913</v>
+        <v>108.7128502820663</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.91371367968008</v>
+        <v>11.02011798017045</v>
       </c>
       <c r="C5" t="n">
-        <v>278.4236489243955</v>
+        <v>140.0463100108075</v>
       </c>
       <c r="D5" t="n">
-        <v>154.9934188079652</v>
+        <v>145.1759417654971</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.64280806657019</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>288.0408494351972</v>
+        <v>289.0471408320502</v>
       </c>
       <c r="D6" t="n">
-        <v>80.82532499523143</v>
+        <v>118.3398682699105</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>184.810078333645</v>
+        <v>400.821080455958</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>68.68994162303657</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>90.29133635957915</v>
+        <v>364.0860448584509</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>35.49999698556465</v>
+        <v>204.5687326293163</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>82.56498192715677</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.706318567709961</v>
+        <v>5.185591373831652</v>
       </c>
       <c r="C2" t="n">
-        <v>8.224100518475531</v>
+        <v>17.24538017279947</v>
       </c>
       <c r="D2" t="n">
-        <v>13.15443748920301</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.7753029489145</v>
+        <v>7.696902001294993</v>
       </c>
       <c r="C3" t="n">
-        <v>17.56837516749667</v>
+        <v>22.87963024747192</v>
       </c>
       <c r="D3" t="n">
-        <v>11.78097245096173</v>
+        <v>11.99695694589602</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39784340465342</v>
+        <v>11.67737182249329</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14165076553849</v>
+        <v>59.94384202213222</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576216871135696</v>
+        <v>0.778491454832886</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.73398742987812</v>
+        <v>2.614394136409256</v>
       </c>
       <c r="C2" t="n">
-        <v>5.572399969304896</v>
+        <v>6.638577976116932</v>
       </c>
       <c r="D2" t="n">
-        <v>28.71219335840221</v>
+        <v>23.26643884294516</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.84602984134927</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="C3" t="n">
-        <v>26.6397239547372</v>
+        <v>52.05226327916589</v>
       </c>
       <c r="D3" t="n">
-        <v>19.98347451994383</v>
+        <v>29.98257488769759</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.12757044828985</v>
+        <v>9.5720401164064</v>
       </c>
       <c r="C4" t="n">
-        <v>27.32498385230147</v>
+        <v>37.16504109196725</v>
       </c>
       <c r="D4" t="n">
-        <v>21.24992905842221</v>
+        <v>20.57350489019616</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4403255290097</v>
+        <v>13.62450634327615</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14076347763304</v>
+        <v>73.73262256361211</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250594848212568</v>
+        <v>1.602883099208959</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.751078051477815</v>
+        <v>2.150027472300514</v>
       </c>
       <c r="C2" t="n">
-        <v>10.16796097288421</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="D2" t="n">
-        <v>28.86141900944773</v>
+        <v>22.37304843208056</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.89726064841935</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C3" t="n">
-        <v>23.89083038284613</v>
+        <v>35.68162031085032</v>
       </c>
       <c r="D3" t="n">
-        <v>38.31270415823177</v>
+        <v>42.27896488338889</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.26491731589317</v>
+        <v>20.21614872585032</v>
       </c>
       <c r="C4" t="n">
-        <v>49.83842220608933</v>
+        <v>93.86980674155878</v>
       </c>
       <c r="D4" t="n">
-        <v>26.49540704221292</v>
+        <v>31.51115606320987</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.70167187109599</v>
+        <v>8.860273030827464</v>
       </c>
       <c r="C5" t="n">
-        <v>31.07231483941155</v>
+        <v>42.58330667170541</v>
       </c>
       <c r="D5" t="n">
-        <v>30.31146036862028</v>
+        <v>27.58711048933538</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73069436440616</v>
+        <v>14.82712770138077</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0572356228776</v>
+        <v>87.31530757479786</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18267359110154</v>
+        <v>2.471187950230128</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.319910882864218</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C2" t="n">
-        <v>7.80882123957913</v>
+        <v>5.393721887131976</v>
       </c>
       <c r="D2" t="n">
-        <v>30.90738122509809</v>
+        <v>20.08459453348124</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.81519475189012</v>
+        <v>9.115527433931634</v>
       </c>
       <c r="C3" t="n">
-        <v>33.09471511015998</v>
+        <v>23.4392264388926</v>
       </c>
       <c r="D3" t="n">
-        <v>51.72337779824321</v>
+        <v>50.36856596638261</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.94508854848696</v>
+        <v>21.09677641655971</v>
       </c>
       <c r="C4" t="n">
-        <v>54.80312034646545</v>
+        <v>91.30449999036186</v>
       </c>
       <c r="D4" t="n">
-        <v>39.01563551447249</v>
+        <v>45.6011991145601</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.30516897176729</v>
+        <v>20.0521968592411</v>
       </c>
       <c r="C5" t="n">
-        <v>63.98540662428588</v>
+        <v>115.8462291011237</v>
       </c>
       <c r="D5" t="n">
-        <v>32.64311116620645</v>
+        <v>32.7658296292373</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.7597749120958</v>
+        <v>8.412596077690921</v>
       </c>
       <c r="C6" t="n">
-        <v>31.27553661419064</v>
+        <v>41.17744395922398</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>33.16736444027425</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05051685944487</v>
+        <v>16.05684611601312</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7581337973308</v>
+        <v>100.5665625160822</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016838953148287</v>
+        <v>3.380388656002763</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.496625469628643</v>
+        <v>1.709222753093697</v>
       </c>
       <c r="C2" t="n">
-        <v>6.742643232767094</v>
+        <v>10.12967281241859</v>
       </c>
       <c r="D2" t="n">
-        <v>26.05951106152733</v>
+        <v>28.93799533037898</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.73803759388213</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C3" t="n">
-        <v>29.57514959043516</v>
+        <v>22.00096605217102</v>
       </c>
       <c r="D3" t="n">
-        <v>59.93569734426777</v>
+        <v>54.10902471956296</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.75967710110456</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="C4" t="n">
-        <v>58.26181750852697</v>
+        <v>72.78579304515428</v>
       </c>
       <c r="D4" t="n">
-        <v>48.21755674637784</v>
+        <v>58.51707191163113</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.53740120931728</v>
+        <v>25.94268308472197</v>
       </c>
       <c r="C5" t="n">
-        <v>62.39006660488482</v>
+        <v>143.8260386721578</v>
       </c>
       <c r="D5" t="n">
-        <v>31.29320807286709</v>
+        <v>41.25794727097221</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.32958949118645</v>
+        <v>17.30821202587127</v>
       </c>
       <c r="C6" t="n">
-        <v>45.56487444950297</v>
+        <v>113.5901728767645</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>35.74347041621788</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>38.5669768136317</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.61021477034756</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051459886523507</v>
+        <v>17.30787893103305</v>
       </c>
       <c r="C21" t="n">
-        <v>66.10743643615787</v>
+        <v>113.3666069982665</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407162429077192</v>
+        <v>4.326969732758262</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.654866776461628</v>
+        <v>1.604175748739288</v>
       </c>
       <c r="C2" t="n">
-        <v>5.43593703841459</v>
+        <v>11.07215060849553</v>
       </c>
       <c r="D2" t="n">
-        <v>30.47835747834223</v>
+        <v>24.29629218470006</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.66502841086936</v>
+        <v>6.877142668248907</v>
       </c>
       <c r="C3" t="n">
-        <v>27.50857067299563</v>
+        <v>31.01340997715674</v>
       </c>
       <c r="D3" t="n">
-        <v>67.34298377280996</v>
+        <v>62.78767442510475</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.27241144462865</v>
+        <v>17.16585860875548</v>
       </c>
       <c r="C4" t="n">
-        <v>68.14016290865837</v>
+        <v>63.63492269386975</v>
       </c>
       <c r="D4" t="n">
-        <v>68.44646819238336</v>
+        <v>69.58235028619694</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.3668391506856</v>
+        <v>27.46439202630453</v>
       </c>
       <c r="C5" t="n">
-        <v>89.06906046779189</v>
+        <v>139.0154749213484</v>
       </c>
       <c r="D5" t="n">
-        <v>41.82245220091413</v>
+        <v>51.61538555077607</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.47300677146449</v>
+        <v>25.23778823307276</v>
       </c>
       <c r="C6" t="n">
-        <v>77.12217265481245</v>
+        <v>166.5211003512313</v>
       </c>
       <c r="D6" t="n">
-        <v>34.5359207399943</v>
+        <v>40.13090090649688</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>13.95358012045992</v>
       </c>
       <c r="C7" t="n">
-        <v>47.19064864773568</v>
+        <v>97.31574118346508</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>24.45042657426681</v>
+        <v>37.1346069131356</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269745845789823</v>
+        <v>17.687994014302</v>
       </c>
       <c r="C21" t="n">
-        <v>75.42361315006941</v>
+        <v>126.4691572022593</v>
       </c>
       <c r="D21" t="n">
-        <v>5.452309384342366</v>
+        <v>5.306398204290599</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.927792638242241</v>
+        <v>1.528581175512284</v>
       </c>
       <c r="C2" t="n">
-        <v>8.947648576505429</v>
+        <v>7.085273181549231</v>
       </c>
       <c r="D2" t="n">
-        <v>29.08623923372025</v>
+        <v>19.40915211295944</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.33828635180442</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C3" t="n">
-        <v>23.699389580518</v>
+        <v>47.32023934469626</v>
       </c>
       <c r="D3" t="n">
-        <v>76.7481267794944</v>
+        <v>68.11856445916494</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.47058561216627</v>
+        <v>13.18388992033042</v>
       </c>
       <c r="C4" t="n">
-        <v>68.59962083424587</v>
+        <v>107.8705107518225</v>
       </c>
       <c r="D4" t="n">
-        <v>85.15286887555135</v>
+        <v>64.78356750783853</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.01251034491051</v>
+        <v>14.21079801897258</v>
       </c>
       <c r="C5" t="n">
-        <v>109.7593933347934</v>
+        <v>99.50012982541426</v>
       </c>
       <c r="D5" t="n">
-        <v>56.91682315370885</v>
+        <v>38.82812170296135</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>8.654106012935635</v>
       </c>
       <c r="C6" t="n">
-        <v>111.9801066417997</v>
+        <v>64.08063615159783</v>
       </c>
       <c r="D6" t="n">
-        <v>39.56737772425921</v>
+        <v>25.43904651244335</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>81.08646988456105</v>
+        <v>26.11056194214817</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>45.06221962492859</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.62343515439249</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.473845597719437</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.08076297434367</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539614898004507</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
